--- a/List of university programs.xlsx
+++ b/List of university programs.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giancarlomanzi/Documents/Box Sync BackUp PC Lavoro 24062015/documenti/Ricerca/Lavori con Russo-Falorsi/paper competenze GenAI vs corsi universitari/SUBMISSION TO QUALITY &amp; QUANTITY/RESUBMISSION 9 marzo 2026/SUBMISSION MANDATA IL 09032026 alle 10.45/Revisioni giugno 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEA6E8B-3171-7D4E-9578-7E861A4F4B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F029CE-6B6F-8745-8197-1D116ACEF1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="32040" windowHeight="20640" xr2:uid="{1D320B99-D9E0-42D0-B75D-954BC5D08805}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$E$212</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="283">
   <si>
     <t>Università</t>
   </si>
@@ -861,6 +864,30 @@
   </si>
   <si>
     <t>Ecodesign , TORINO</t>
+  </si>
+  <si>
+    <t>[LM-51] - Psicologia</t>
+  </si>
+  <si>
+    <t>Neuroscienze Cognitive e Riabilitazione Psicologica , ROMA</t>
+  </si>
+  <si>
+    <t>[LM-29] - Ingegneria elettronica</t>
+  </si>
+  <si>
+    <t>Ingegneria elettronica , BARI</t>
+  </si>
+  <si>
+    <t>[L-4] - Disegno industriale</t>
+  </si>
+  <si>
+    <t>Design della Comunicazione , MILANO</t>
+  </si>
+  <si>
+    <t>[L-8] - Ingegneria dell'informazione</t>
+  </si>
+  <si>
+    <t>Ingegneria elettronica e delle comunicazioni</t>
   </si>
 </sst>
 </file>
@@ -939,25 +966,25 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1274,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2CB644-1026-45DE-9CA1-5BA5743A1C07}">
-  <dimension ref="A1:E208"/>
+  <dimension ref="A1:E212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.33203125" style="3" customWidth="1"/>
@@ -1613,16 +1640,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>123</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1633,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1650,13 +1677,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1673,7 +1700,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1684,13 +1711,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1701,13 +1728,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1715,16 +1742,16 @@
         <v>18</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1735,13 +1762,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1749,16 +1776,16 @@
         <v>18</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1766,16 +1793,16 @@
         <v>18</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1786,13 +1813,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1803,13 +1830,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1820,13 +1847,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1834,16 +1861,16 @@
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1854,13 +1881,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1877,7 +1904,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1888,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1911,7 +1938,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1919,19 +1946,19 @@
         <v>18</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>18</v>
       </c>
@@ -1939,16 +1966,16 @@
         <v>30</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>18</v>
       </c>
@@ -1956,13 +1983,13 @@
         <v>30</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1973,47 +2000,47 @@
         <v>30</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
+    <row r="43" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="D43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -2021,16 +2048,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -2041,13 +2068,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -2058,13 +2085,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -2072,16 +2099,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -2092,13 +2119,13 @@
         <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -2109,13 +2136,13 @@
         <v>10</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -2126,13 +2153,13 @@
         <v>10</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -2140,16 +2167,16 @@
         <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -2160,13 +2187,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -2177,13 +2204,13 @@
         <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -2191,16 +2218,16 @@
         <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -2211,81 +2238,81 @@
         <v>10</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="5" t="s">
+      <c r="D57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="B58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="5" t="s">
+      <c r="D58" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="28" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>12</v>
+        <v>279</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2302,7 +2329,7 @@
         <v>8</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2319,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2330,13 +2357,13 @@
         <v>10</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2347,13 +2374,13 @@
         <v>10</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2364,13 +2391,13 @@
         <v>10</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2381,13 +2408,13 @@
         <v>10</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2398,13 +2425,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2415,13 +2442,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2432,13 +2459,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2455,7 +2482,7 @@
         <v>15</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2472,7 +2499,7 @@
         <v>15</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2489,7 +2516,7 @@
         <v>15</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2506,7 +2533,7 @@
         <v>15</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2523,7 +2550,7 @@
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2540,41 +2567,41 @@
         <v>15</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2585,13 +2612,13 @@
         <v>19</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2599,16 +2626,16 @@
         <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2616,16 +2643,16 @@
         <v>49</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2636,13 +2663,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2653,13 +2680,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2676,7 +2703,7 @@
         <v>8</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2687,13 +2714,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2704,13 +2731,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2721,13 +2748,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2738,13 +2765,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2755,13 +2782,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2772,13 +2799,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2789,13 +2816,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2806,13 +2833,13 @@
         <v>6</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2829,7 +2856,7 @@
         <v>8</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2837,16 +2864,16 @@
         <v>49</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2854,16 +2881,16 @@
         <v>49</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2871,16 +2898,16 @@
         <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>12</v>
+        <v>275</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>192</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2891,13 +2918,13 @@
         <v>10</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2908,13 +2935,13 @@
         <v>10</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2925,13 +2952,13 @@
         <v>10</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2942,13 +2969,13 @@
         <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2959,13 +2986,13 @@
         <v>10</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2976,13 +3003,13 @@
         <v>10</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -2993,13 +3020,13 @@
         <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3007,16 +3034,16 @@
         <v>49</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3024,16 +3051,16 @@
         <v>49</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3041,16 +3068,16 @@
         <v>49</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3058,16 +3085,16 @@
         <v>49</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3075,16 +3102,16 @@
         <v>49</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3092,16 +3119,16 @@
         <v>49</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3112,13 +3139,13 @@
         <v>6</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3129,13 +3156,13 @@
         <v>6</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3146,13 +3173,13 @@
         <v>6</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3163,13 +3190,13 @@
         <v>6</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3180,13 +3207,13 @@
         <v>6</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3197,13 +3224,13 @@
         <v>6</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3214,13 +3241,13 @@
         <v>6</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3231,13 +3258,13 @@
         <v>6</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3248,13 +3275,13 @@
         <v>6</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3262,16 +3289,16 @@
         <v>49</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3279,16 +3306,16 @@
         <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3296,16 +3323,16 @@
         <v>49</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3316,13 +3343,13 @@
         <v>10</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3333,13 +3360,13 @@
         <v>10</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3350,13 +3377,13 @@
         <v>10</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3367,13 +3394,13 @@
         <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3384,13 +3411,13 @@
         <v>10</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3401,13 +3428,13 @@
         <v>10</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3424,7 +3451,7 @@
         <v>15</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3441,7 +3468,7 @@
         <v>15</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3449,16 +3476,16 @@
         <v>49</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3466,16 +3493,16 @@
         <v>49</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3483,16 +3510,16 @@
         <v>49</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3503,13 +3530,13 @@
         <v>30</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3520,64 +3547,64 @@
         <v>30</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3588,13 +3615,13 @@
         <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3605,13 +3632,13 @@
         <v>10</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3622,13 +3649,13 @@
         <v>10</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3639,13 +3666,13 @@
         <v>10</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3656,13 +3683,13 @@
         <v>10</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3673,13 +3700,13 @@
         <v>10</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="28" x14ac:dyDescent="0.2">
@@ -3690,64 +3717,64 @@
         <v>10</v>
       </c>
       <c r="C142" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A143" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E142" s="5" t="s">
+      <c r="D143" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A144" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A145" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E145" s="5" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -3755,16 +3782,16 @@
         <v>71</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -3772,16 +3799,16 @@
         <v>71</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -3792,13 +3819,13 @@
         <v>6</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -3806,16 +3833,16 @@
         <v>71</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -3823,16 +3850,16 @@
         <v>71</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -3840,16 +3867,16 @@
         <v>71</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -3860,13 +3887,13 @@
         <v>10</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -3877,13 +3904,13 @@
         <v>10</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -3894,13 +3921,13 @@
         <v>10</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -3911,13 +3938,13 @@
         <v>10</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -3928,13 +3955,13 @@
         <v>10</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
@@ -3942,16 +3969,16 @@
         <v>71</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
@@ -3959,16 +3986,16 @@
         <v>71</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
@@ -3976,16 +4003,16 @@
         <v>71</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
@@ -3993,16 +4020,16 @@
         <v>71</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -4010,16 +4037,16 @@
         <v>71</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -4027,16 +4054,16 @@
         <v>71</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -4047,13 +4074,13 @@
         <v>6</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
@@ -4064,13 +4091,13 @@
         <v>6</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
@@ -4081,13 +4108,13 @@
         <v>6</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -4095,16 +4122,16 @@
         <v>71</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -4112,16 +4139,16 @@
         <v>71</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -4129,16 +4156,16 @@
         <v>71</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -4149,13 +4176,13 @@
         <v>10</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -4166,13 +4193,13 @@
         <v>10</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -4183,13 +4210,13 @@
         <v>10</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -4200,13 +4227,13 @@
         <v>10</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -4217,30 +4244,30 @@
         <v>10</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -4248,67 +4275,67 @@
         <v>71</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -4319,13 +4346,13 @@
         <v>6</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -4333,16 +4360,16 @@
         <v>75</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -4353,13 +4380,13 @@
         <v>6</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
@@ -4370,13 +4397,13 @@
         <v>6</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
@@ -4387,13 +4414,13 @@
         <v>6</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
@@ -4401,16 +4428,16 @@
         <v>75</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
@@ -4421,13 +4448,13 @@
         <v>6</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
@@ -4438,13 +4465,13 @@
         <v>6</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
@@ -4455,13 +4482,13 @@
         <v>6</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
@@ -4469,76 +4496,84 @@
         <v>75</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C189" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="D189" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>84</v>
+        <v>264</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C190" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="D190" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C191" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="D191" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>86</v>
+        <v>273</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C192" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="D192" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>88</v>
+        <v>274</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
@@ -4546,14 +4581,14 @@
         <v>82</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C193" s="6"/>
       <c r="D193" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
@@ -4561,14 +4596,14 @@
         <v>82</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
@@ -4576,14 +4611,14 @@
         <v>82</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C195" s="6"/>
       <c r="D195" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
@@ -4591,14 +4626,14 @@
         <v>82</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
@@ -4606,14 +4641,14 @@
         <v>82</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C197" s="6"/>
       <c r="D197" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
@@ -4621,14 +4656,14 @@
         <v>82</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
@@ -4636,14 +4671,14 @@
         <v>82</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C199" s="6"/>
       <c r="D199" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
@@ -4651,14 +4686,14 @@
         <v>82</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
@@ -4666,14 +4701,14 @@
         <v>82</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C201" s="6"/>
       <c r="D201" s="5" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
@@ -4681,14 +4716,14 @@
         <v>82</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
@@ -4696,14 +4731,14 @@
         <v>82</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C203" s="6"/>
       <c r="D203" s="5" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
@@ -4711,14 +4746,14 @@
         <v>82</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
@@ -4726,14 +4761,14 @@
         <v>82</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C205" s="6"/>
       <c r="D205" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
@@ -4741,14 +4776,14 @@
         <v>82</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
@@ -4756,22 +4791,83 @@
         <v>82</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C207" s="6"/>
       <c r="D207" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E207" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C208" s="6"/>
+      <c r="D208" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A209" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C209" s="6"/>
+      <c r="D209" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A210" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C210" s="6"/>
+      <c r="D210" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A211" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C211" s="6"/>
+      <c r="D211" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E211" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A208" s="4"/>
-      <c r="B208" s="4"/>
-      <c r="D208" s="4"/>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A212" s="4"/>
+      <c r="B212" s="4"/>
+      <c r="D212" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E212" xr:uid="{DC2CB644-1026-45DE-9CA1-5BA5743A1C07}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>